--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.38759349454428</v>
+        <v>8.675483942863446</v>
       </c>
       <c r="D2" t="n">
-        <v>53.30823401745315</v>
+        <v>8.662588027836136</v>
       </c>
       <c r="E2" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F2" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.08047084123237</v>
+        <v>9.43807651170026</v>
       </c>
       <c r="D3" t="n">
-        <v>58.18915953345219</v>
+        <v>9.455738424185981</v>
       </c>
       <c r="E3" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F3" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.84753316545942</v>
+        <v>6.962724139387156</v>
       </c>
       <c r="D4" t="n">
-        <v>42.51952263551667</v>
+        <v>6.909422428271458</v>
       </c>
       <c r="E4" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F4" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.75458121523315</v>
+        <v>8.085119447475387</v>
       </c>
       <c r="D5" t="n">
-        <v>36.28015986734347</v>
+        <v>5.895525978443314</v>
       </c>
       <c r="E5" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F5" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.64973808362891</v>
+        <v>8.555582438589699</v>
       </c>
       <c r="D6" t="n">
-        <v>52.14129607222864</v>
+        <v>8.472960611737154</v>
       </c>
       <c r="E6" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F6" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.78618926499874</v>
+        <v>7.765255755562295</v>
       </c>
       <c r="D7" t="n">
-        <v>37.03039292257105</v>
+        <v>6.017438849917795</v>
       </c>
       <c r="E7" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F7" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>54.76183291650852</v>
+        <v>8.898797848932634</v>
       </c>
       <c r="D8" t="n">
-        <v>54.21416702882451</v>
+        <v>8.809802142183983</v>
       </c>
       <c r="E8" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F8" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.08255030608264</v>
+        <v>6.35091442473843</v>
       </c>
       <c r="D9" t="n">
-        <v>38.53992195706743</v>
+        <v>6.262737318023459</v>
       </c>
       <c r="E9" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F9" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.40063489398322</v>
+        <v>5.265103170272273</v>
       </c>
       <c r="D10" t="n">
-        <v>31.85680631133618</v>
+        <v>5.176731025592129</v>
       </c>
       <c r="E10" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F10" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.14247381456725</v>
+        <v>5.223151994867179</v>
       </c>
       <c r="D11" t="n">
-        <v>24.24423483802403</v>
+        <v>3.939688161178905</v>
       </c>
       <c r="E11" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F11" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>10.49812752615428</v>
+        <v>1.705945723000071</v>
       </c>
       <c r="D12" t="n">
-        <v>4.097242993189852</v>
+        <v>0.665801986393351</v>
       </c>
       <c r="E12" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F12" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25487845301538</v>
+        <v>3.128917748614999</v>
       </c>
       <c r="D13" t="n">
-        <v>3.859859360016555</v>
+        <v>0.6272271460026903</v>
       </c>
       <c r="E13" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F13" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>19.88559433730418</v>
+        <v>3.231409079811929</v>
       </c>
       <c r="D14" t="n">
-        <v>7.706519951507186</v>
+        <v>1.252309492119918</v>
       </c>
       <c r="E14" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F14" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>41.42209278111576</v>
+        <v>6.731090076931311</v>
       </c>
       <c r="D15" t="n">
-        <v>41.28647697692018</v>
+        <v>6.70905250874953</v>
       </c>
       <c r="E15" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F15" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>47.45263128397335</v>
+        <v>7.71105258364567</v>
       </c>
       <c r="D16" t="n">
-        <v>47.38699779671342</v>
+        <v>7.700387141965932</v>
       </c>
       <c r="E16" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F16" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>52.91587729047763</v>
+        <v>8.598830059702616</v>
       </c>
       <c r="D17" t="n">
-        <v>52.93772253968859</v>
+        <v>8.602379912699396</v>
       </c>
       <c r="E17" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F17" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>31.6675965218328</v>
+        <v>5.14598443479783</v>
       </c>
       <c r="D18" t="n">
-        <v>31.3958599864513</v>
+        <v>5.101827247798337</v>
       </c>
       <c r="E18" t="n">
-        <v>13.64527149081884</v>
+        <v>2.217356617258062</v>
       </c>
       <c r="F18" t="n">
-        <v>16.98652406871859</v>
+        <v>2.760310161166772</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
